--- a/src/modules/hrm/templates/attendance_template.xlsx
+++ b/src/modules/hrm/templates/attendance_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Website\ERP\Erp-backend\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Website\ERP\Erp-backend\src\modules\hrm\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B7D4DD1-DE79-43F3-ACDB-BD99B7C2E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2959C0-6453-4FEB-A733-B57B836CCF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CDA568F0-1519-4B44-BFD1-6AD33F766F7A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="10">
   <si>
     <t xml:space="preserve">Attendace of month </t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Out</t>
+  </si>
+  <si>
+    <t>Employee Code</t>
   </si>
 </sst>
 </file>
@@ -105,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -152,21 +155,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -177,10 +228,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -495,471 +554,478 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA43685-621B-4144-AADB-001F035985EA}">
-  <dimension ref="A1:BO4"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="9" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:68" s="4" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="11"/>
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7">
         <v>2</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7">
         <v>3</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7">
         <v>4</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5">
+      <c r="J2" s="7"/>
+      <c r="K2" s="7">
         <v>5</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5">
+      <c r="L2" s="7"/>
+      <c r="M2" s="7">
         <v>6</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5">
-        <v>7</v>
-      </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5">
+      <c r="N2" s="7"/>
+      <c r="O2" s="7">
+        <v>7</v>
+      </c>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7">
+        <v>8</v>
+      </c>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7">
         <v>9</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5">
+      <c r="T2" s="7"/>
+      <c r="U2" s="7">
         <v>10</v>
       </c>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5">
+      <c r="V2" s="7"/>
+      <c r="W2" s="7">
         <v>11</v>
       </c>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5">
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7">
         <v>12</v>
       </c>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5">
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7">
         <v>13</v>
       </c>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5">
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7">
         <v>14</v>
       </c>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5">
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7">
         <v>15</v>
       </c>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5">
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7">
         <v>16</v>
       </c>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5">
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7">
         <v>17</v>
       </c>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5">
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7">
         <v>18</v>
       </c>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5">
+      <c r="AL2" s="7"/>
+      <c r="AM2" s="7">
         <v>19</v>
       </c>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5">
+      <c r="AN2" s="7"/>
+      <c r="AO2" s="7">
         <v>20</v>
       </c>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5">
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7">
         <v>21</v>
       </c>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5">
+      <c r="AR2" s="7"/>
+      <c r="AS2" s="7">
         <v>22</v>
       </c>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5">
+      <c r="AT2" s="7"/>
+      <c r="AU2" s="7">
         <v>23</v>
       </c>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5">
+      <c r="AV2" s="7"/>
+      <c r="AW2" s="7">
         <v>24</v>
       </c>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5">
+      <c r="AX2" s="7"/>
+      <c r="AY2" s="7">
         <v>25</v>
       </c>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5">
+      <c r="AZ2" s="7"/>
+      <c r="BA2" s="7">
         <v>26</v>
       </c>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5">
+      <c r="BB2" s="7"/>
+      <c r="BC2" s="7">
         <v>27</v>
       </c>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5">
+      <c r="BD2" s="7"/>
+      <c r="BE2" s="7">
         <v>28</v>
       </c>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5">
+      <c r="BF2" s="7"/>
+      <c r="BG2" s="7">
         <v>29</v>
       </c>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5">
+      <c r="BH2" s="7"/>
+      <c r="BI2" s="7">
         <v>30</v>
       </c>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5">
+      <c r="BJ2" s="7"/>
+      <c r="BK2" s="7">
         <v>31</v>
       </c>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="1" t="s">
+      <c r="BL2" s="7"/>
+      <c r="BM2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BN2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BO2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BP2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="5"/>
-      <c r="AK3" s="5"/>
-      <c r="AL3" s="5"/>
-      <c r="AM3" s="5"/>
-      <c r="AN3" s="5"/>
-      <c r="AO3" s="5"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="5"/>
-      <c r="AR3" s="5"/>
-      <c r="AS3" s="5"/>
-      <c r="AT3" s="5"/>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="5"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="2"/>
-      <c r="BM3" s="2"/>
-      <c r="BN3" s="2"/>
-      <c r="BO3" s="2"/>
+    <row r="3" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="7"/>
+      <c r="AO3" s="7"/>
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7"/>
+      <c r="AT3" s="7"/>
+      <c r="AU3" s="7"/>
+      <c r="AV3" s="7"/>
+      <c r="AW3" s="7"/>
+      <c r="AX3" s="7"/>
+      <c r="AY3" s="7"/>
+      <c r="AZ3" s="7"/>
+      <c r="BA3" s="7"/>
+      <c r="BB3" s="7"/>
+      <c r="BC3" s="7"/>
+      <c r="BD3" s="7"/>
+      <c r="BE3" s="7"/>
+      <c r="BF3" s="7"/>
+      <c r="BG3" s="7"/>
+      <c r="BH3" s="7"/>
+      <c r="BI3" s="7"/>
+      <c r="BJ3" s="7"/>
+      <c r="BK3" s="7"/>
+      <c r="BL3" s="7"/>
+      <c r="BM3" s="6"/>
+      <c r="BN3" s="6"/>
+      <c r="BO3" s="6"/>
+      <c r="BP3" s="6"/>
     </row>
-    <row r="4" spans="1:67" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:68" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AY4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BB4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BC4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BD4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BE4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BF4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BG4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BH4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BI4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BJ4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="BK4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL4" s="2"/>
-      <c r="BM4" s="2"/>
-      <c r="BN4" s="2"/>
-      <c r="BO4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="6"/>
+      <c r="BO4" s="6"/>
+      <c r="BP4" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="BO2:BO4"/>
-    <mergeCell ref="BF2:BG3"/>
-    <mergeCell ref="BH2:BI3"/>
-    <mergeCell ref="BJ2:BK3"/>
-    <mergeCell ref="BL2:BL4"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="AG2:AH3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+    <mergeCell ref="O2:P3"/>
+    <mergeCell ref="Q2:R3"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="W2:X3"/>
+    <mergeCell ref="Y2:Z3"/>
+    <mergeCell ref="AA2:AB3"/>
+    <mergeCell ref="AC2:AD3"/>
+    <mergeCell ref="AE2:AF3"/>
+    <mergeCell ref="BE2:BF3"/>
+    <mergeCell ref="AI2:AJ3"/>
+    <mergeCell ref="AK2:AL3"/>
+    <mergeCell ref="AM2:AN3"/>
+    <mergeCell ref="AO2:AP3"/>
+    <mergeCell ref="AQ2:AR3"/>
+    <mergeCell ref="AS2:AT3"/>
+    <mergeCell ref="AU2:AV3"/>
+    <mergeCell ref="AW2:AX3"/>
+    <mergeCell ref="AY2:AZ3"/>
+    <mergeCell ref="BA2:BB3"/>
+    <mergeCell ref="BC2:BD3"/>
+    <mergeCell ref="BP2:BP4"/>
+    <mergeCell ref="BG2:BH3"/>
+    <mergeCell ref="BI2:BJ3"/>
+    <mergeCell ref="BK2:BL3"/>
     <mergeCell ref="BM2:BM4"/>
     <mergeCell ref="BN2:BN4"/>
-    <mergeCell ref="AT2:AU3"/>
-    <mergeCell ref="AV2:AW3"/>
-    <mergeCell ref="AX2:AY3"/>
-    <mergeCell ref="AZ2:BA3"/>
-    <mergeCell ref="BB2:BC3"/>
-    <mergeCell ref="BD2:BE3"/>
-    <mergeCell ref="AH2:AI3"/>
-    <mergeCell ref="AJ2:AK3"/>
-    <mergeCell ref="AL2:AM3"/>
-    <mergeCell ref="AN2:AO3"/>
-    <mergeCell ref="AP2:AQ3"/>
-    <mergeCell ref="AR2:AS3"/>
-    <mergeCell ref="V2:W3"/>
-    <mergeCell ref="X2:Y3"/>
-    <mergeCell ref="Z2:AA3"/>
-    <mergeCell ref="AB2:AC3"/>
-    <mergeCell ref="AD2:AE3"/>
-    <mergeCell ref="AF2:AG3"/>
-    <mergeCell ref="J2:K3"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="N2:O3"/>
-    <mergeCell ref="P2:Q3"/>
-    <mergeCell ref="R2:S3"/>
-    <mergeCell ref="T2:U3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:E3"/>
-    <mergeCell ref="F2:G3"/>
-    <mergeCell ref="H2:I3"/>
+    <mergeCell ref="BO2:BO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
